--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_304_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_304_R31.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.266</v>
+        <v>4.0964</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5894</v>
+        <v>1.8567</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6767</v>
+        <v>2.2398</v>
       </c>
       <c r="G2" t="n">
         <v>1.6095</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1331</v>
+        <v>-0.0365</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1019</v>
+        <v>0.1654</v>
       </c>
       <c r="U2" t="n">
-        <v>0.235</v>
+        <v>-0.2018</v>
       </c>
       <c r="V2" t="n">
         <v>4.147</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0726</v>
+        <v>1.9395</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8175</v>
+        <v>1.8187</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2552</v>
+        <v>0.1207</v>
       </c>
       <c r="G3" t="n">
         <v>1.1796</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2694</v>
+        <v>1.1362</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3397</v>
+        <v>1.341</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0703</v>
+        <v>-0.2047</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6864</v>
+        <v>1.7543</v>
       </c>
       <c r="E4" t="n">
-        <v>1.986</v>
+        <v>2.2219</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2996</v>
+        <v>-0.4676</v>
       </c>
       <c r="G4" t="n">
         <v>0.5719</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1867</v>
+        <v>0.2546</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1336</v>
+        <v>0.1024</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.241</v>
+        <v>1.3832</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8989</v>
+        <v>0.6865</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6579</v>
+        <v>0.6967</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4448</v>
+        <v>0.9913</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9329</v>
+        <v>-0.742</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5119</v>
+        <v>1.7332</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5506</v>
+        <v>1.7351</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2499</v>
+        <v>0.3634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6993</v>
+        <v>1.3717</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8942</v>
+        <v>-0.7438</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-1.1053</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2112</v>
+        <v>0.3615</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4333</v>
+        <v>-0.2732</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4495</v>
+        <v>0.3738</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0163</v>
+        <v>-0.6471</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7886</v>
+        <v>3.2166</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0025</v>
+        <v>0.0361</v>
       </c>
       <c r="E6" t="n">
         <v>-0.0411</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0436</v>
+        <v>0.0772</v>
       </c>
       <c r="G6" t="n">
         <v>0.4519</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4494</v>
+        <v>-0.4158</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3747</v>
+        <v>-0.3411</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0129</v>
+        <v>-0.2752</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6424</v>
+        <v>0.4835</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6294999999999999</v>
+        <v>-0.7587</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9913</v>
+        <v>-2.4448</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.742</v>
+        <v>-1.9329</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7332</v>
+        <v>-0.5119</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7351</v>
+        <v>-0.5506</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3634</v>
+        <v>-1.2499</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3717</v>
+        <v>0.6993</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7438</v>
+        <v>-1.8942</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1053</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3615</v>
+        <v>-1.2112</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6693</v>
+        <v>0.917</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.955</v>
+        <v>1.0341</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7143</v>
+        <v>-0.1171</v>
       </c>
       <c r="V7" t="n">
-        <v>3.2166</v>
+        <v>0.7886</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8428</v>
+        <v>-1.2297</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3006</v>
+        <v>-0.7932</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4578</v>
+        <v>-0.4365</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8222</v>
+        <v>-1.4678</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8152</v>
+        <v>-0.8355</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.007</v>
+        <v>-0.6323</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.486</v>
+        <v>-1.2497</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1709</v>
+        <v>-0.4131</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3151</v>
+        <v>-0.8366</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3363</v>
+        <v>-0.2181</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6443</v>
+        <v>-0.4223</v>
       </c>
       <c r="O8" t="n">
-        <v>0.308</v>
+        <v>0.2042</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8017</v>
+        <v>-0.4551</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3451</v>
+        <v>0.3148</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5434</v>
+        <v>-0.7699</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.214</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BAIOCCHI</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8154</v>
+        <v>-1.2347</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0618</v>
+        <v>-1.5916</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2465</v>
+        <v>0.357</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5133</v>
+        <v>-1.8222</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.617</v>
+        <v>-0.8152</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1038</v>
+        <v>-1.007</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7527</v>
+        <v>-1.486</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7527</v>
+        <v>-0.1709</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.3151</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2395</v>
+        <v>-0.3363</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1357</v>
+        <v>-0.6443</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1038</v>
+        <v>0.308</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1423</v>
+        <v>0.4099</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>1.0541</v>
       </c>
       <c r="U9" t="n">
-        <v>0.007</v>
+        <v>-0.6442</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>M. BAIOCCHI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0009</v>
+        <v>-1.3271</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2254</v>
+        <v>-1.708</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7755</v>
+        <v>0.3809</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1059</v>
+        <v>-0.5133</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7407</v>
+        <v>-0.617</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3652</v>
+        <v>0.1038</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0013</v>
+        <v>-0.7527</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.215</v>
+        <v>-0.7527</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1045</v>
+        <v>0.2395</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5256999999999999</v>
+        <v>0.1357</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5788</v>
+        <v>0.1038</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3589</v>
+        <v>0.3459</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>0.2045</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1349</v>
+        <v>0.1415</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1369</v>
+        <v>-1.7314</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5323</v>
+        <v>-0.9895</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6045</v>
+        <v>-0.7419</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4678</v>
+        <v>-2.1059</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8355</v>
+        <v>-0.7407</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6323</v>
+        <v>-1.3652</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2497</v>
+        <v>-1.0013</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4131</v>
+        <v>-0.215</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8366</v>
+        <v>-0.7863</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2181</v>
+        <v>-1.1045</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4223</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2042</v>
+        <v>-0.5788</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3623</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4244</v>
+        <v>0.0119</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9379</v>
+        <v>-0.1013</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.547</v>
+        <v>-2.1624</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3044</v>
+        <v>-0.1551</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2426</v>
+        <v>-2.0073</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0551</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5821</v>
+        <v>-0.1975</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1019</v>
+        <v>0.0474</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4802</v>
+        <v>-0.2449</v>
       </c>
       <c r="V12" t="n">
         <v>0.3943</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3355</v>
+        <v>-4.1781</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2239</v>
+        <v>-2.3354</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1116</v>
+        <v>-1.8427</v>
       </c>
       <c r="G13" t="n">
         <v>-5.9949</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1808</v>
+        <v>-0.0235</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3102</v>
+        <v>0.5783</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8707</v>
+        <v>-0.6018</v>
       </c>
       <c r="V13" t="n">
         <v>1.6083</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.422899999999998</v>
+        <v>-2.929099999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.040099999999999</v>
+        <v>-0.5465999999999993</v>
       </c>
       <c r="F14" t="n">
         <v>-2.382400000000001</v>
@@ -1519,13 +1519,13 @@
         <v>-1.3214</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.3936</v>
+        <v>-2.393599999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-2.9613</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5677000000000001</v>
+        <v>0.5677000000000003</v>
       </c>
       <c r="M14" t="n">
         <v>-10.2062</v>
@@ -1537,7 +1537,7 @@
         <v>-1.8893</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>1.159799999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.9172</v>
@@ -1546,16 +1546,16 @@
         <v>15.077</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07909999999999995</v>
+        <v>1.5726</v>
       </c>
       <c r="T14" t="n">
-        <v>3.659199999999999</v>
+        <v>5.153</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5804</v>
+        <v>-3.5802</v>
       </c>
       <c r="V14" t="n">
-        <v>6.938200000000001</v>
+        <v>6.9382</v>
       </c>
       <c r="W14" t="n">
         <v>10.6113</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.8668</v>
+        <v>7.5599</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3586</v>
+        <v>6.0612</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5082</v>
+        <v>1.4987</v>
       </c>
       <c r="G15" t="n">
         <v>4.381</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0219</v>
+        <v>1.715</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3397</v>
+        <v>1.0422</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6822</v>
+        <v>0.6728</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0486</v>
+        <v>5.4012</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9962</v>
+        <v>2.3501</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0523</v>
+        <v>3.0511</v>
       </c>
       <c r="G16" t="n">
         <v>2.4179</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9054</v>
+        <v>0.4472</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2126</v>
+        <v>0.5665</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.118</v>
+        <v>-0.1193</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3629</v>
+        <v>3.0884</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8124</v>
+        <v>1.4585</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5506</v>
+        <v>1.6299</v>
       </c>
       <c r="G17" t="n">
         <v>1.5487</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5153</v>
+        <v>0.2407</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9164</v>
+        <v>0.5625</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4011</v>
+        <v>-0.3218</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7886</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3169</v>
+        <v>2.036</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0736</v>
+        <v>1.5454</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2433</v>
+        <v>0.4906</v>
       </c>
       <c r="G18" t="n">
         <v>2.2181</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3831</v>
+        <v>0.3361</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2794</v>
+        <v>0.7512</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6625</v>
+        <v>-0.4151</v>
       </c>
       <c r="V18" t="n">
         <v>-1.214</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9152</v>
+        <v>-0.4219</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8148</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1004</v>
+        <v>0.393</v>
       </c>
       <c r="G19" t="n">
         <v>2.3989</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9946</v>
+        <v>-0.5012</v>
       </c>
       <c r="T19" t="n">
         <v>0.0474</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.042</v>
+        <v>-0.5487</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9525</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0973</v>
+        <v>0.3745</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8552</v>
+        <v>-1.1241</v>
       </c>
       <c r="G20" t="n">
         <v>-0.208</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3681</v>
+        <v>-0.1652</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5149</v>
+        <v>-0.0431</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1467</v>
+        <v>-0.1221</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0015</v>
+        <v>-1.6041</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8548</v>
+        <v>-2.663</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1466</v>
+        <v>1.059</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5125</v>
+        <v>0.7645</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1716</v>
+        <v>1.8153</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6591</v>
+        <v>-1.0508</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7805</v>
+        <v>0.3323</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5965</v>
+        <v>1.7981</v>
       </c>
       <c r="L21" t="n">
-        <v>0.184</v>
+        <v>-1.4658</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2679</v>
+        <v>0.4322</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5752</v>
+        <v>0.0171</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8431</v>
+        <v>0.415</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7834</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.0953</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2072</v>
+        <v>0.4839</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2188</v>
+        <v>-0.3886</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.719</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3633</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3558</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7322</v>
+        <v>-2.3274</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0169</v>
+        <v>-1.5626</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2847</v>
+        <v>-0.7649</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7645</v>
+        <v>1.5125</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8153</v>
+        <v>2.1716</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0508</v>
+        <v>-0.6591</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3323</v>
+        <v>1.7805</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7981</v>
+        <v>1.5965</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4658</v>
+        <v>0.184</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4322</v>
+        <v>-0.2679</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0171</v>
+        <v>0.5752</v>
       </c>
       <c r="O22" t="n">
-        <v>0.415</v>
+        <v>-0.8431</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0328</v>
+        <v>0.6625</v>
       </c>
       <c r="T22" t="n">
-        <v>0.13</v>
+        <v>0.4995</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1628</v>
+        <v>0.163</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-1.719</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3633</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1744</v>
+        <v>-2.6526</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6645</v>
+        <v>-3.3107</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4901</v>
+        <v>0.6581</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0599</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1867</v>
+        <v>0.3352</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2161</v>
+        <v>0.1377</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0294</v>
+        <v>0.1975</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3966</v>
+        <v>-2.7619</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4099</v>
+        <v>-1.0561</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9867</v>
+        <v>-1.7058</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3738</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7341</v>
+        <v>-0.0993</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8215</v>
+        <v>-0.4676</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.3684</v>
       </c>
       <c r="V24" t="n">
         <v>-3.2166</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.422799999999997</v>
+        <v>7.5681</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3826</v>
+        <v>2.3825</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0403</v>
+        <v>5.185599999999999</v>
       </c>
       <c r="G25" t="n">
         <v>12.5999</v>
@@ -2404,13 +2404,13 @@
         <v>13.9174</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0791999999999996</v>
+        <v>3.0663</v>
       </c>
       <c r="T25" t="n">
         <v>3.5802</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.6595</v>
+        <v>-0.5139</v>
       </c>
       <c r="V25" t="n">
         <v>-6.9382</v>
